--- a/data/trans_orig/IP12-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP12-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2397</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10763</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2665</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>10597</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17003</t>
+          <t>17207</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80104</t>
+          <t>80231</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88470</t>
+          <t>88685</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76549</t>
+          <t>76248</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84180</t>
+          <t>84106</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160709</t>
+          <t>160505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>170973</t>
+          <t>171511</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22420</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38453</t>
+          <t>38585</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24469</t>
+          <t>24467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42402</t>
+          <t>41453</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50245</t>
+          <t>50541</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74489</t>
+          <t>74675</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>377634</t>
+          <t>377502</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>393667</t>
+          <t>393955</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>434589</t>
+          <t>435538</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>452522</t>
+          <t>452524</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>818589</t>
+          <t>818403</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>842833</t>
+          <t>842537</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13509</t>
+          <t>13849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15800</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13064</t>
+          <t>12598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25970</t>
+          <t>25803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160557</t>
+          <t>160217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>169500</t>
+          <t>169143</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>142338</t>
+          <t>142840</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>152249</t>
+          <t>152223</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>306235</t>
+          <t>306402</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319141</t>
+          <t>319607</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34289</t>
+          <t>34365</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55048</t>
+          <t>55556</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37181</t>
+          <t>38468</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57591</t>
+          <t>59830</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77124</t>
+          <t>76992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106296</t>
+          <t>106453</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>625973</t>
+          <t>625465</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>646732</t>
+          <t>646656</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>664383</t>
+          <t>662144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>684793</t>
+          <t>683506</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1296699</t>
+          <t>1296542</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1325871</t>
+          <t>1326003</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15704</t>
+          <t>15414</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>12461</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24572</t>
+          <t>24779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76665</t>
+          <t>76955</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86283</t>
+          <t>86496</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73205</t>
+          <t>73731</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82552</t>
+          <t>82446</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>153989</t>
+          <t>153782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>167203</t>
+          <t>167163</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26378</t>
+          <t>26245</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44339</t>
+          <t>44907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35868</t>
+          <t>36393</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58080</t>
+          <t>57446</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65559</t>
+          <t>66566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95215</t>
+          <t>97074</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>407871</t>
+          <t>407303</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>425832</t>
+          <t>425965</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>436366</t>
+          <t>437000</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>458578</t>
+          <t>458053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>851441</t>
+          <t>849582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>881097</t>
+          <t>880090</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23563</t>
+          <t>23358</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19003</t>
+          <t>18890</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19782</t>
+          <t>19526</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36561</t>
+          <t>36455</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143249</t>
+          <t>143454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>156423</t>
+          <t>156192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153225</t>
+          <t>153338</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165698</t>
+          <t>165435</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>302480</t>
+          <t>302586</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319259</t>
+          <t>319515</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50187</t>
+          <t>49428</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74651</t>
+          <t>74848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51779</t>
+          <t>52058</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78100</t>
+          <t>76160</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107765</t>
+          <t>107994</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143394</t>
+          <t>146824</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>636740</t>
+          <t>636543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>661204</t>
+          <t>661963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>674766</t>
+          <t>676706</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>701087</t>
+          <t>700808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1320863</t>
+          <t>1317433</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1356492</t>
+          <t>1356263</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>11832</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>14696</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47859</t>
+          <t>47546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56134</t>
+          <t>55909</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62363</t>
+          <t>62660</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67960</t>
+          <t>67948</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113938</t>
+          <t>113297</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122776</t>
+          <t>122867</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25020</t>
+          <t>24164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42281</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27324</t>
+          <t>28364</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46257</t>
+          <t>47827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57376</t>
+          <t>56884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82886</t>
+          <t>81122</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>429392</t>
+          <t>429202</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>446653</t>
+          <t>447509</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>442478</t>
+          <t>440908</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>461411</t>
+          <t>460371</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>877522</t>
+          <t>879286</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>903032</t>
+          <t>903524</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>10925</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23410</t>
+          <t>24629</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5281</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15968</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18969</t>
+          <t>19150</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36154</t>
+          <t>35768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149293</t>
+          <t>148074</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>161577</t>
+          <t>161778</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171527</t>
+          <t>171131</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>182214</t>
+          <t>181950</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324043</t>
+          <t>324429</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>341228</t>
+          <t>341047</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44576</t>
+          <t>44619</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67704</t>
+          <t>68026</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38826</t>
+          <t>38294</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61026</t>
+          <t>60359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90269</t>
+          <t>89092</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121541</t>
+          <t>121457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>636050</t>
+          <t>635728</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>659178</t>
+          <t>659135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>683818</t>
+          <t>684485</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>706018</t>
+          <t>706550</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1327057</t>
+          <t>1327141</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1358329</t>
+          <t>1359506</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12495</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47425</t>
+          <t>46518</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53470</t>
+          <t>53243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49509</t>
+          <t>49333</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58473</t>
+          <t>58410</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99848</t>
+          <t>100208</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110921</t>
+          <t>110666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23071</t>
+          <t>22287</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41612</t>
+          <t>41373</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28522</t>
+          <t>28563</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51069</t>
+          <t>50975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56743</t>
+          <t>56942</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>85198</t>
+          <t>86881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>418082</t>
+          <t>418321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>436623</t>
+          <t>437407</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>465550</t>
+          <t>465644</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>488097</t>
+          <t>488056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>891115</t>
+          <t>889432</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>919570</t>
+          <t>919371</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17704</t>
+          <t>18423</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22140</t>
+          <t>21623</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>17980</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35461</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131847</t>
+          <t>131128</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142212</t>
+          <t>141949</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161209</t>
+          <t>161726</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>175044</t>
+          <t>175454</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>297439</t>
+          <t>298658</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>315289</t>
+          <t>314920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36460</t>
+          <t>37102</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59621</t>
+          <t>59086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47607</t>
+          <t>45885</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74856</t>
+          <t>72733</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89398</t>
+          <t>89319</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126919</t>
+          <t>124694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>604302</t>
+          <t>604837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>627463</t>
+          <t>626821</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>687116</t>
+          <t>689239</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>714365</t>
+          <t>716087</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1298976</t>
+          <t>1301201</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1336497</t>
+          <t>1336576</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP12-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP12-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>5504</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10399</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>5653</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2182</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10636</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2710</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10815</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,22%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5504</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2739</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10597</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6898</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17207</t>
+          <t>18085</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>81341</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>76446</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>84098</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,66%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,03%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>85214</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>80231</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>88685</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>80052</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>88157</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,78%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,29%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>81341</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>76248</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>84106</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,66%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160505</t>
+          <t>159627</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171511</t>
+          <t>170814</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>32033</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24565</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>41467</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,72%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>29627</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>22132</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>38585</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>21106</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>38107</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,12%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>32033</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>24467</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>41453</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,72%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50541</t>
+          <t>49816</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74675</t>
+          <t>73349</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>444958</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>435524</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>452426</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,28%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>583</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>386460</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>377502</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>393955</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>377980</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>394981</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,88%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>444958</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>435538</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>452524</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,28%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>818403</t>
+          <t>819729</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>842537</t>
+          <t>843262</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9856</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5824</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15909</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8597</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4923</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13849</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4883</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13926</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9856</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5915</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15298</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12598</t>
+          <t>12733</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25803</t>
+          <t>26146</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148282</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>142229</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>152314</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,94%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,32%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>165469</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>160217</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>169143</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>160140</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>169183</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,06%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>148282</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>142840</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>152223</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,77%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>306402</t>
+          <t>306059</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319607</t>
+          <t>319472</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,17%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>47392</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>38238</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>60195</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,56%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>43878</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34365</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>55556</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>34308</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>55512</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,44%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>47392</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>38468</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>59830</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76992</t>
+          <t>77948</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106453</t>
+          <t>106589</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1014</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>674582</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>661779</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>683736</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,66%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>951</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>637143</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>625465</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>646656</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>625509</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>646713</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,56%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1014</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>674582</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>662144</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>683506</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,44%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1296542</t>
+          <t>1296406</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1326003</t>
+          <t>1325047</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7048</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3644</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12272</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10061</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5873</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15414</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5795</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15128</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>10,89%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7048</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3746</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12461</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11466</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24779</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>79144</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>73920</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>82548</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,76%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,77%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>82308</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>76955</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>86496</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>77241</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>86574</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>89,11%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,64%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>79144</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>73731</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>82446</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,82%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>153782</t>
+          <t>154017</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>167163</t>
+          <t>167095</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>45295</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>34883</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56452</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,16%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>35049</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>26245</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>44907</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>26345</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>46247</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,75%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>45295</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>36393</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>57446</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66566</t>
+          <t>66715</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97074</t>
+          <t>95633</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>449151</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>437994</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>459563</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,84%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,95%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>605</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>417161</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>407303</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>425965</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>405963</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>425865</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,25%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>449151</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>437000</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>458053</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,84%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>849582</t>
+          <t>851023</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>880090</t>
+          <t>879941</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>655</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>452210</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,107 +3012,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11218</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6534</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18367</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>16181</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10620</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23358</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>23689</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,7%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11218</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6793</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18890</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>27399</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>19419</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>37181</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>10,97%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>27399</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>19526</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>36455</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -3125,107 +3125,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>161010</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>153861</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165694</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>150631</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>143454</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>156192</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>143123</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>155970</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,3%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>161010</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>153338</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165435</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>85,8%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>93,5%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>311642</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>301860</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>319622</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>91,92%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>89,03%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>96,06%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>311642</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>302586</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>319515</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>91,92%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>89,25%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3360,67 +3360,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>63560</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>51571</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>78151</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>61292</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>49428</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>74848</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>50093</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>73802</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,62%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,95%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>63560</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>52058</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>76160</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107994</t>
+          <t>108873</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146824</t>
+          <t>145132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>689306</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>674715</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>701295</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,62%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>937</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>650099</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>636543</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>661963</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>637589</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>661298</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,38%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,48%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,05%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>689306</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>676706</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>700808</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,56%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1317433</t>
+          <t>1319125</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1356263</t>
+          <t>1355384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1073</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>752866</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>752866</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2239</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6615</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6580</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3469</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11832</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3496</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11673</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,08%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,93%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2239</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>666</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5954</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>15065</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66375</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61999</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>67943</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,74%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>90,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52798</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>47546</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>55909</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>47705</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>55882</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>88,92%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>80,07%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>66375</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>62660</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>67948</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,74%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113297</t>
+          <t>112928</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122867</t>
+          <t>123132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>36370</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>28286</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>47115</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,64%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>32420</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>24164</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>42471</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>24324</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>42024</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,87%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>36370</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>28364</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>47827</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,44%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56884</t>
+          <t>56454</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81122</t>
+          <t>82124</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>452365</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>441620</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>460449</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,56%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,21%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>663</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>439253</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>429202</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>447509</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>429649</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>447349</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,13%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,88%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>452365</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>440908</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>460371</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,56%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>879286</t>
+          <t>878284</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>903524</t>
+          <t>903954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>713</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>471673</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>471673</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>471673</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9873</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5679</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16400</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>16726</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10925</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24629</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>11002</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>24019</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,68%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9873</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5545</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>16364</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19150</t>
+          <t>19318</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35768</t>
+          <t>36008</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>177622</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>171095</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>181816</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,25%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155977</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>148074</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>161778</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>148684</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>161701</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,32%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>85,74%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,67%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>177622</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>171131</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>181950</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324429</t>
+          <t>324189</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>341047</t>
+          <t>340879</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>48482</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37665</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>59976</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>55726</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>44619</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>68026</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>43970</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>67739</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,92%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>48482</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>38294</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>60359</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89092</t>
+          <t>87932</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121457</t>
+          <t>121156</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>696362</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>684868</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>707179</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,49%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,95%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,94%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>975</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>648028</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>635728</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>659135</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>636015</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>659784</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,08%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>995</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>696362</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>684485</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>706550</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1327141</t>
+          <t>1327442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1359506</t>
+          <t>1360666</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>703754</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>703754</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>703754</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12392</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,68%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3560</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1435</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8160</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3317</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1229</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>2,63%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,92%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6831</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3594</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12671</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,02%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10391</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>16449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50107</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44340</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>53333</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,32%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,16%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>51118</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>46518</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>53243</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,08%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>43441</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>39350</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>92,91%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>84,16%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>97,37%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>55173</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>49333</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>58410</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,98%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>79,56%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>137</t>
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>106291</t>
+          <t>93548</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100208</t>
+          <t>87041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110666</t>
+          <t>97557</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>36302</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>27282</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>49617</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,43%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>32015</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>22287</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>41373</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,96%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38702</t>
+          <t>31381</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28563</t>
+          <t>23645</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50975</t>
+          <t>40913</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>70717</t>
+          <t>67683</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56942</t>
+          <t>55059</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86881</t>
+          <t>81198</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>439376</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>426061</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>448396</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,37%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,26%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>590</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>427679</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>418321</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>437407</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,15%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>477917</t>
+          <t>400221</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>465644</t>
+          <t>390689</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>488056</t>
+          <t>407957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>905596</t>
+          <t>839597</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>889432</t>
+          <t>826082</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>919371</t>
+          <t>852221</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>459694</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>431602</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>976313</t>
+          <t>907280</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12477</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6988</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20328</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11697</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7602</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18423</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>11950</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25268</t>
+          <t>24427</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17980</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34242</t>
+          <t>34352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>155942</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>148091</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>161431</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,59%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>137854</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>131128</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>141949</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>92,18%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>87,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>94,92%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>169779</t>
+          <t>138026</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161726</t>
+          <t>131513</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>175454</t>
+          <t>142655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>307632</t>
+          <t>293968</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>298658</t>
+          <t>284043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>314920</t>
+          <t>301003</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>55404</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43666</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>70112</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>47272</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>37102</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>59086</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>46649</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45885</t>
+          <t>35618</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72733</t>
+          <t>57963</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>106375</t>
+          <t>102053</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89319</t>
+          <t>85554</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124694</t>
+          <t>121135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>645425</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>630717</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>657163</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,09%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>864</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>616651</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>604837</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>626821</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>702869</t>
+          <t>581687</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>689239</t>
+          <t>570373</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>716087</t>
+          <t>592718</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1319520</t>
+          <t>1227112</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1301201</t>
+          <t>1208030</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1336576</t>
+          <t>1243611</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663923</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628336</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1425895</t>
+          <t>1329165</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1425895</t>
+          <t>1329165</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1425895</t>
+          <t>1329165</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
